--- a/data/coa_taxonomy.xlsx
+++ b/data/coa_taxonomy.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="64">
   <si>
     <t>category</t>
   </si>
@@ -89,7 +89,7 @@
     <t>kewajiban</t>
   </si>
   <si>
-    <t>kewajiban_jk_pendek</t>
+    <t>kewajiban_jangka_pendek</t>
   </si>
   <si>
     <t>Kewajiban</t>
@@ -101,12 +101,24 @@
     <t>kredit</t>
   </si>
   <si>
-    <t>kewajiban_jk_panjang</t>
+    <t>kewajiban_jangka_panjang</t>
   </si>
   <si>
     <t>Kewajiban Jangka Panjang</t>
   </si>
   <si>
+    <t>utang_bagi_hasil_bumdes</t>
+  </si>
+  <si>
+    <t>Utang Bagi Hasil BUMDES</t>
+  </si>
+  <si>
+    <t>utang_bagi_hasil_unit</t>
+  </si>
+  <si>
+    <t>Utang Bagi Hasil Unit Usaha</t>
+  </si>
+  <si>
     <t>ekuitas</t>
   </si>
   <si>
@@ -141,12 +153,6 @@
   </si>
   <si>
     <t>Ikhtisar Laba Rugi</t>
-  </si>
-  <si>
-    <t>saldo_laba</t>
-  </si>
-  <si>
-    <t>Saldo Laba</t>
   </si>
   <si>
     <t>laba_dicadangkan</t>
@@ -841,7 +847,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -850,9 +856,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1382,11 +1385,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.7142857142857" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24.4285714285714" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7142857142857" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.7142857142857" style="1" customWidth="1"/>
     <col min="4" max="4" width="42.7142857142857" style="1" customWidth="1"/>
     <col min="5" max="5" width="18.2857142857143" style="1" customWidth="1"/>
@@ -1417,19 +1420,19 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="1">
@@ -1443,13 +1446,13 @@
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="1">
@@ -1463,13 +1466,13 @@
       <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F4" s="1">
@@ -1480,16 +1483,16 @@
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="1">
@@ -1500,16 +1503,16 @@
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F6" s="1">
@@ -1520,16 +1523,16 @@
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F7" s="1">
@@ -1540,16 +1543,16 @@
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F8" s="1">
@@ -1558,58 +1561,58 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F11" s="1">
@@ -1618,18 +1621,18 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F12" s="1">
@@ -1637,19 +1640,19 @@
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="3" t="s">
+      <c r="A13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="3" t="s">
+      <c r="C13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F13" s="1">
@@ -1657,79 +1660,79 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="3" t="s">
+      <c r="A14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="3" t="s">
+      <c r="C14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="C16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F17" s="1">
@@ -1738,19 +1741,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>10</v>
+      <c r="E18" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1758,18 +1761,18 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F19" s="1">
@@ -1778,18 +1781,18 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F20" s="1">
@@ -1798,18 +1801,18 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F21" s="1">
@@ -1818,21 +1821,41 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="1">
         <v>0</v>
       </c>
     </row>

--- a/data/coa_taxonomy.xlsx
+++ b/data/coa_taxonomy.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="66">
   <si>
     <t>category</t>
   </si>
@@ -159,6 +159,12 @@
   </si>
   <si>
     <t>Laba Dicadangkan</t>
+  </si>
+  <si>
+    <t>saldo_laba</t>
+  </si>
+  <si>
+    <t>Saldo Laba</t>
   </si>
   <si>
     <t>pendapatan</t>
@@ -1385,7 +1391,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.7142857142857" style="1" customWidth="1"/>
@@ -1721,16 +1727,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>23</v>
@@ -1741,13 +1747,13 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>49</v>
@@ -1761,19 +1767,19 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="E19" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -1781,13 +1787,13 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>55</v>
@@ -1801,16 +1807,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="C21" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>10</v>
@@ -1821,13 +1827,13 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>61</v>
@@ -1841,13 +1847,13 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>63</v>
@@ -1856,6 +1862,26 @@
         <v>10</v>
       </c>
       <c r="F23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="1">
         <v>0</v>
       </c>
     </row>
